--- a/features/quotation/data/BKK_PTT.xlsx
+++ b/features/quotation/data/BKK_PTT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LAND CONTRACTS\DIVINE Tours &amp; Travels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHAKH NAIR\Desktop\Work\VIKRAM\features\quotation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538A8105-661F-4534-9D26-BF84F4D9A74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF5FA4B-485B-4DFE-8CFB-445C09B0A0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B27EDA18-C4A4-44CA-9B7D-115C474DD462}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{B27EDA18-C4A4-44CA-9B7D-115C474DD462}"/>
   </bookViews>
   <sheets>
     <sheet name="TRANSFER" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="253">
   <si>
     <t>Suvarnbhumi Airport to Bangkok Hotel</t>
   </si>
@@ -1168,6 +1168,12 @@
       </rPr>
       <t>For Breakfast</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Colosseum Show </t>
+  </si>
+  <si>
+    <t>Attraction</t>
   </si>
 </sst>
 </file>
@@ -1637,24 +1643,24 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:G84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="99" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="7.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="7.109375" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" s="18" t="s">
         <v>186</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>181</v>
       </c>
@@ -1677,7 +1683,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1700,7 +1706,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -1723,7 +1729,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -1746,7 +1752,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -1769,7 +1775,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -1792,7 +1798,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -1815,7 +1821,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -1838,7 +1844,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -1861,7 +1867,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -1884,7 +1890,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -1907,7 +1913,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -1930,7 +1936,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -1953,7 +1959,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -1976,7 +1982,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -1999,7 +2005,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -2022,7 +2028,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -2045,7 +2051,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -2068,7 +2074,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -2091,7 +2097,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -2114,7 +2120,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -2137,7 +2143,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -2160,7 +2166,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -2183,7 +2189,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -2206,7 +2212,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -2229,7 +2235,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -2252,7 +2258,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -2275,7 +2281,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -2298,7 +2304,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -2321,7 +2327,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -2344,7 +2350,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -2367,7 +2373,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -2390,7 +2396,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -2413,7 +2419,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -2436,7 +2442,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -2459,7 +2465,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -2482,7 +2488,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -2505,7 +2511,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -2528,7 +2534,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -2551,7 +2557,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -2574,7 +2580,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>40</v>
       </c>
@@ -2597,7 +2603,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>41</v>
       </c>
@@ -2620,7 +2626,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>42</v>
       </c>
@@ -2643,7 +2649,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43</v>
       </c>
@@ -2666,7 +2672,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>44</v>
       </c>
@@ -2689,7 +2695,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>45</v>
       </c>
@@ -2712,7 +2718,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -2735,7 +2741,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>47</v>
       </c>
@@ -2758,7 +2764,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>48</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>49</v>
       </c>
@@ -2804,7 +2810,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>50</v>
       </c>
@@ -2827,7 +2833,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>51</v>
       </c>
@@ -2850,7 +2856,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>52</v>
       </c>
@@ -2873,7 +2879,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>53</v>
       </c>
@@ -2896,7 +2902,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>54</v>
       </c>
@@ -2919,7 +2925,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>55</v>
       </c>
@@ -2942,7 +2948,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>56</v>
       </c>
@@ -2965,7 +2971,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>57</v>
       </c>
@@ -2988,7 +2994,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>58</v>
       </c>
@@ -3011,7 +3017,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>59</v>
       </c>
@@ -3034,7 +3040,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>60</v>
       </c>
@@ -3057,7 +3063,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>61</v>
       </c>
@@ -3080,7 +3086,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>62</v>
       </c>
@@ -3103,7 +3109,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>63</v>
       </c>
@@ -3126,7 +3132,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>64</v>
       </c>
@@ -3149,7 +3155,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>65</v>
       </c>
@@ -3172,7 +3178,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>66</v>
       </c>
@@ -3195,7 +3201,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>67</v>
       </c>
@@ -3218,7 +3224,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>68</v>
       </c>
@@ -3241,7 +3247,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>69</v>
       </c>
@@ -3264,7 +3270,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>70</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>71</v>
       </c>
@@ -3310,7 +3316,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>72</v>
       </c>
@@ -3333,7 +3339,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>73</v>
       </c>
@@ -3356,7 +3362,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>74</v>
       </c>
@@ -3379,7 +3385,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>75</v>
       </c>
@@ -3402,7 +3408,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>76</v>
       </c>
@@ -3425,7 +3431,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>77</v>
       </c>
@@ -3448,7 +3454,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>78</v>
       </c>
@@ -3471,7 +3477,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>79</v>
       </c>
@@ -3494,12 +3500,12 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B83" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B84" s="7" t="s">
         <v>185</v>
       </c>
@@ -3519,24 +3525,24 @@
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
   <dimension ref="A1:G104"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="119.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="119.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="7.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="7.109375" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" s="18" t="s">
         <v>186</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>181</v>
       </c>
@@ -3559,7 +3565,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -3582,7 +3588,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -3605,7 +3611,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -3628,7 +3634,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -3651,7 +3657,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -3674,7 +3680,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -3697,7 +3703,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -3720,7 +3726,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -3743,7 +3749,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -3766,7 +3772,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -3789,7 +3795,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -3812,7 +3818,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -3835,7 +3841,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -3858,7 +3864,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -3881,7 +3887,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -3904,7 +3910,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -3927,7 +3933,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -3950,7 +3956,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -3973,7 +3979,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -3996,7 +4002,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -4019,7 +4025,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -4042,7 +4048,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -4065,7 +4071,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -4088,7 +4094,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -4111,7 +4117,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -4134,7 +4140,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -4157,7 +4163,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -4180,7 +4186,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -4203,7 +4209,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -4226,7 +4232,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -4249,7 +4255,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -4272,7 +4278,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -4295,7 +4301,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -4318,7 +4324,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -4341,7 +4347,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -4364,7 +4370,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -4387,7 +4393,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -4410,7 +4416,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -4433,7 +4439,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -4456,7 +4462,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>40</v>
       </c>
@@ -4479,7 +4485,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>41</v>
       </c>
@@ -4502,7 +4508,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>42</v>
       </c>
@@ -4525,7 +4531,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43</v>
       </c>
@@ -4548,7 +4554,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>44</v>
       </c>
@@ -4571,7 +4577,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>45</v>
       </c>
@@ -4594,7 +4600,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>46</v>
       </c>
@@ -4617,7 +4623,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>47</v>
       </c>
@@ -4640,7 +4646,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>48</v>
       </c>
@@ -4663,7 +4669,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>49</v>
       </c>
@@ -4686,7 +4692,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>50</v>
       </c>
@@ -4709,7 +4715,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>51</v>
       </c>
@@ -4732,7 +4738,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>52</v>
       </c>
@@ -4755,7 +4761,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>53</v>
       </c>
@@ -4778,7 +4784,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>54</v>
       </c>
@@ -4801,7 +4807,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>55</v>
       </c>
@@ -4824,7 +4830,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>56</v>
       </c>
@@ -4847,7 +4853,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>57</v>
       </c>
@@ -4870,7 +4876,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>58</v>
       </c>
@@ -4893,7 +4899,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>59</v>
       </c>
@@ -4916,7 +4922,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>60</v>
       </c>
@@ -4939,7 +4945,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>61</v>
       </c>
@@ -4962,7 +4968,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>62</v>
       </c>
@@ -4985,7 +4991,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>63</v>
       </c>
@@ -5008,7 +5014,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>64</v>
       </c>
@@ -5031,7 +5037,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>65</v>
       </c>
@@ -5054,7 +5060,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>66</v>
       </c>
@@ -5077,7 +5083,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>67</v>
       </c>
@@ -5100,7 +5106,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>68</v>
       </c>
@@ -5123,7 +5129,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>69</v>
       </c>
@@ -5146,7 +5152,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>70</v>
       </c>
@@ -5169,7 +5175,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>71</v>
       </c>
@@ -5192,7 +5198,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>72</v>
       </c>
@@ -5215,7 +5221,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>73</v>
       </c>
@@ -5238,7 +5244,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>74</v>
       </c>
@@ -5261,7 +5267,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>75</v>
       </c>
@@ -5284,7 +5290,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>76</v>
       </c>
@@ -5307,7 +5313,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>77</v>
       </c>
@@ -5330,7 +5336,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>78</v>
       </c>
@@ -5353,7 +5359,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>79</v>
       </c>
@@ -5376,7 +5382,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>80</v>
       </c>
@@ -5399,7 +5405,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>81</v>
       </c>
@@ -5422,7 +5428,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>82</v>
       </c>
@@ -5445,7 +5451,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>83</v>
       </c>
@@ -5468,7 +5474,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>84</v>
       </c>
@@ -5491,7 +5497,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>85</v>
       </c>
@@ -5514,7 +5520,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>86</v>
       </c>
@@ -5537,7 +5543,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>87</v>
       </c>
@@ -5560,7 +5566,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>88</v>
       </c>
@@ -5583,7 +5589,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>89</v>
       </c>
@@ -5606,7 +5612,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>90</v>
       </c>
@@ -5629,7 +5635,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>91</v>
       </c>
@@ -5652,7 +5658,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>92</v>
       </c>
@@ -5675,7 +5681,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>93</v>
       </c>
@@ -5698,7 +5704,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>94</v>
       </c>
@@ -5721,7 +5727,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>95</v>
       </c>
@@ -5744,7 +5750,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>96</v>
       </c>
@@ -5767,7 +5773,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>97</v>
       </c>
@@ -5790,7 +5796,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>98</v>
       </c>
@@ -5813,12 +5819,35 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>99</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E101" s="3">
+        <v>215</v>
+      </c>
+      <c r="F101" s="3">
+        <v>215</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>185</v>
       </c>
@@ -5838,26 +5867,26 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="105.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.109375" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" s="18" t="s">
         <v>186</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>181</v>
       </c>
@@ -5880,7 +5909,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -5903,7 +5932,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -5926,7 +5955,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -5949,7 +5978,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -5972,7 +6001,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -5995,7 +6024,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -6018,7 +6047,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -6041,7 +6070,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -6064,7 +6093,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -6087,7 +6116,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -6110,7 +6139,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -6133,7 +6162,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -6156,7 +6185,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -6179,7 +6208,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -6202,7 +6231,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -6225,7 +6254,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -6248,7 +6277,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>17</v>
       </c>
@@ -6271,7 +6300,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>18</v>
       </c>
@@ -6294,7 +6323,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>19</v>
       </c>
@@ -6317,7 +6346,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>20</v>
       </c>
@@ -6340,7 +6369,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>21</v>
       </c>
@@ -6363,7 +6392,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>22</v>
       </c>
@@ -6386,7 +6415,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>23</v>
       </c>
@@ -6409,7 +6438,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>24</v>
       </c>
@@ -6432,7 +6461,7 @@
         <v>2750</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>25</v>
       </c>
@@ -6455,7 +6484,7 @@
         <v>2850</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>26</v>
       </c>
@@ -6478,7 +6507,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>27</v>
       </c>
@@ -6501,7 +6530,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>28</v>
       </c>
@@ -6524,7 +6553,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>29</v>
       </c>
@@ -6547,7 +6576,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>30</v>
       </c>
@@ -6570,7 +6599,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>31</v>
       </c>
@@ -6593,7 +6622,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>32</v>
       </c>
@@ -6616,7 +6645,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>33</v>
       </c>
@@ -6639,7 +6668,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>34</v>
       </c>
@@ -6662,7 +6691,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>35</v>
       </c>
@@ -6685,7 +6714,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>36</v>
       </c>
@@ -6708,7 +6737,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>37</v>
       </c>
@@ -6731,7 +6760,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>38</v>
       </c>
@@ -6754,7 +6783,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>39</v>
       </c>
@@ -6777,12 +6806,12 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
         <v>185</v>
       </c>
@@ -6801,24 +6830,24 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="77" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="7.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="7.109375" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E1" s="18" t="s">
         <v>186</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
     </row>
-    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>181</v>
       </c>
@@ -6841,7 +6870,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -6864,7 +6893,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -6887,7 +6916,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3</v>
       </c>
@@ -6910,7 +6939,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>4</v>
       </c>
@@ -6933,7 +6962,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>5</v>
       </c>
@@ -6956,7 +6985,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>6</v>
       </c>
@@ -6979,7 +7008,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>7</v>
       </c>
@@ -7002,7 +7031,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>8</v>
       </c>
@@ -7025,7 +7054,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>9</v>
       </c>
@@ -7048,7 +7077,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>10</v>
       </c>
@@ -7071,7 +7100,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>11</v>
       </c>
@@ -7094,7 +7123,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>12</v>
       </c>
@@ -7117,7 +7146,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>13</v>
       </c>
@@ -7140,7 +7169,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>14</v>
       </c>
@@ -7163,7 +7192,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>15</v>
       </c>
@@ -7186,7 +7215,7 @@
         <v>2700</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>16</v>
       </c>
@@ -7209,12 +7238,12 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>185</v>
       </c>
